--- a/site/public/downloads/ken/ken-white-collar.xlsx
+++ b/site/public/downloads/ken/ken-white-collar.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>台灣個人／家庭通膨每年 10% 起跳。官方 CPI 約 2% 左右，但房租、外食、醫療與照護的實際漲幅常遠高於 CPI；本工具採保守的 10% 起跳假設，讓規劃留足安全邊際。通膨格子設有驗證，低於 10% 會被拒絕，公式也以 MAX(10%, 輸入值) 計算。</t>
+          <t>台灣個人／家庭通膨每年 5% 起跳。官方 CPI 約 2% 左右，但房租、外食、醫療與照護的實際漲幅常遠高於 CPI；本工具採保守的 5% 起跳假設，讓規劃留足安全邊際。通膨格子設有驗證，低於 5% 會被拒絕，公式也以 MAX(5%, 輸入值) 計算。</t>
         </is>
       </c>
     </row>
@@ -792,15 +792,15 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>個人／家庭通膨（10% 起跳）</t>
+          <t>個人／家庭通膨（5% 起跳）</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>不可低於 10%</t>
+          <t>不可低於 5%</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>(1+$B$9)/(1+MAX(0.1,$B$11))-1</f>
+        <f>(1+$B$9)/(1+MAX(0.05,$B$11))-1</f>
         <v/>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -910,7 +910,7 @@
         <v/>
       </c>
       <c r="C18" s="15">
-        <f>C17*(1+MAX(0.1,$B$11))</f>
+        <f>C17*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D18" s="15">
@@ -936,7 +936,7 @@
         <v/>
       </c>
       <c r="C19" s="15">
-        <f>C18*(1+MAX(0.1,$B$11))</f>
+        <f>C18*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D19" s="15">
@@ -962,7 +962,7 @@
         <v/>
       </c>
       <c r="C20" s="15">
-        <f>C19*(1+MAX(0.1,$B$11))</f>
+        <f>C19*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D20" s="15">
@@ -988,7 +988,7 @@
         <v/>
       </c>
       <c r="C21" s="15">
-        <f>C20*(1+MAX(0.1,$B$11))</f>
+        <f>C20*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D21" s="15">
@@ -1014,7 +1014,7 @@
         <v/>
       </c>
       <c r="C22" s="15">
-        <f>C21*(1+MAX(0.1,$B$11))</f>
+        <f>C21*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D22" s="15">
@@ -1040,7 +1040,7 @@
         <v/>
       </c>
       <c r="C23" s="15">
-        <f>C22*(1+MAX(0.1,$B$11))</f>
+        <f>C22*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D23" s="15">
@@ -1066,7 +1066,7 @@
         <v/>
       </c>
       <c r="C24" s="15">
-        <f>C23*(1+MAX(0.1,$B$11))</f>
+        <f>C23*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D24" s="15">
@@ -1092,7 +1092,7 @@
         <v/>
       </c>
       <c r="C25" s="15">
-        <f>C24*(1+MAX(0.1,$B$11))</f>
+        <f>C24*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D25" s="15">
@@ -1118,7 +1118,7 @@
         <v/>
       </c>
       <c r="C26" s="15">
-        <f>C25*(1+MAX(0.1,$B$11))</f>
+        <f>C25*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D26" s="15">
@@ -1144,7 +1144,7 @@
         <v/>
       </c>
       <c r="C27" s="15">
-        <f>C26*(1+MAX(0.1,$B$11))</f>
+        <f>C26*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D27" s="15">
@@ -1170,7 +1170,7 @@
         <v/>
       </c>
       <c r="C28" s="15">
-        <f>C27*(1+MAX(0.1,$B$11))</f>
+        <f>C27*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D28" s="15">
@@ -1196,7 +1196,7 @@
         <v/>
       </c>
       <c r="C29" s="15">
-        <f>C28*(1+MAX(0.1,$B$11))</f>
+        <f>C28*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D29" s="15">
@@ -1222,7 +1222,7 @@
         <v/>
       </c>
       <c r="C30" s="15">
-        <f>C29*(1+MAX(0.1,$B$11))</f>
+        <f>C29*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D30" s="15">
@@ -1248,7 +1248,7 @@
         <v/>
       </c>
       <c r="C31" s="15">
-        <f>C30*(1+MAX(0.1,$B$11))</f>
+        <f>C30*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D31" s="15">
@@ -1274,7 +1274,7 @@
         <v/>
       </c>
       <c r="C32" s="15">
-        <f>C31*(1+MAX(0.1,$B$11))</f>
+        <f>C31*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D32" s="15">
@@ -1300,7 +1300,7 @@
         <v/>
       </c>
       <c r="C33" s="15">
-        <f>C32*(1+MAX(0.1,$B$11))</f>
+        <f>C32*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D33" s="15">
@@ -1326,7 +1326,7 @@
         <v/>
       </c>
       <c r="C34" s="15">
-        <f>C33*(1+MAX(0.1,$B$11))</f>
+        <f>C33*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D34" s="15">
@@ -1352,7 +1352,7 @@
         <v/>
       </c>
       <c r="C35" s="15">
-        <f>C34*(1+MAX(0.1,$B$11))</f>
+        <f>C34*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D35" s="15">
@@ -1378,7 +1378,7 @@
         <v/>
       </c>
       <c r="C36" s="15">
-        <f>C35*(1+MAX(0.1,$B$11))</f>
+        <f>C35*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D36" s="15">
@@ -1404,7 +1404,7 @@
         <v/>
       </c>
       <c r="C37" s="15">
-        <f>C36*(1+MAX(0.1,$B$11))</f>
+        <f>C36*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D37" s="15">
@@ -1430,7 +1430,7 @@
         <v/>
       </c>
       <c r="C38" s="15">
-        <f>C37*(1+MAX(0.1,$B$11))</f>
+        <f>C37*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D38" s="15">
@@ -1456,7 +1456,7 @@
         <v/>
       </c>
       <c r="C39" s="15">
-        <f>C38*(1+MAX(0.1,$B$11))</f>
+        <f>C38*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D39" s="15">
@@ -1482,7 +1482,7 @@
         <v/>
       </c>
       <c r="C40" s="15">
-        <f>C39*(1+MAX(0.1,$B$11))</f>
+        <f>C39*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D40" s="15">
@@ -1508,7 +1508,7 @@
         <v/>
       </c>
       <c r="C41" s="15">
-        <f>C40*(1+MAX(0.1,$B$11))</f>
+        <f>C40*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D41" s="15">
@@ -1534,7 +1534,7 @@
         <v/>
       </c>
       <c r="C42" s="15">
-        <f>C41*(1+MAX(0.1,$B$11))</f>
+        <f>C41*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D42" s="15">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C43" s="15">
-        <f>C42*(1+MAX(0.1,$B$11))</f>
+        <f>C42*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D43" s="15">
@@ -1586,7 +1586,7 @@
         <v/>
       </c>
       <c r="C44" s="15">
-        <f>C43*(1+MAX(0.1,$B$11))</f>
+        <f>C43*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D44" s="15">
@@ -1612,7 +1612,7 @@
         <v/>
       </c>
       <c r="C45" s="15">
-        <f>C44*(1+MAX(0.1,$B$11))</f>
+        <f>C44*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D45" s="15">
@@ -1638,7 +1638,7 @@
         <v/>
       </c>
       <c r="C46" s="15">
-        <f>C45*(1+MAX(0.1,$B$11))</f>
+        <f>C45*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D46" s="15">
@@ -1664,7 +1664,7 @@
         <v/>
       </c>
       <c r="C47" s="15">
-        <f>C46*(1+MAX(0.1,$B$11))</f>
+        <f>C46*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D47" s="15">
@@ -1690,7 +1690,7 @@
         <v/>
       </c>
       <c r="C48" s="15">
-        <f>C47*(1+MAX(0.1,$B$11))</f>
+        <f>C47*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D48" s="15">
@@ -1716,7 +1716,7 @@
         <v/>
       </c>
       <c r="C49" s="15">
-        <f>C48*(1+MAX(0.1,$B$11))</f>
+        <f>C48*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D49" s="15">
@@ -1742,7 +1742,7 @@
         <v/>
       </c>
       <c r="C50" s="15">
-        <f>C49*(1+MAX(0.1,$B$11))</f>
+        <f>C49*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D50" s="15">
@@ -1768,7 +1768,7 @@
         <v/>
       </c>
       <c r="C51" s="15">
-        <f>C50*(1+MAX(0.1,$B$11))</f>
+        <f>C50*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D51" s="15">
@@ -1794,7 +1794,7 @@
         <v/>
       </c>
       <c r="C52" s="15">
-        <f>C51*(1+MAX(0.1,$B$11))</f>
+        <f>C51*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D52" s="15">
@@ -1820,7 +1820,7 @@
         <v/>
       </c>
       <c r="C53" s="15">
-        <f>C52*(1+MAX(0.1,$B$11))</f>
+        <f>C52*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D53" s="15">
@@ -1846,7 +1846,7 @@
         <v/>
       </c>
       <c r="C54" s="15">
-        <f>C53*(1+MAX(0.1,$B$11))</f>
+        <f>C53*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D54" s="15">
@@ -1872,7 +1872,7 @@
         <v/>
       </c>
       <c r="C55" s="15">
-        <f>C54*(1+MAX(0.1,$B$11))</f>
+        <f>C54*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D55" s="15">
@@ -1898,7 +1898,7 @@
         <v/>
       </c>
       <c r="C56" s="15">
-        <f>C55*(1+MAX(0.1,$B$11))</f>
+        <f>C55*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D56" s="15">
@@ -1924,7 +1924,7 @@
         <v/>
       </c>
       <c r="C57" s="15">
-        <f>C56*(1+MAX(0.1,$B$11))</f>
+        <f>C56*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D57" s="15">
@@ -1950,7 +1950,7 @@
         <v/>
       </c>
       <c r="C58" s="15">
-        <f>C57*(1+MAX(0.1,$B$11))</f>
+        <f>C57*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D58" s="15">
@@ -1976,7 +1976,7 @@
         <v/>
       </c>
       <c r="C59" s="15">
-        <f>C58*(1+MAX(0.1,$B$11))</f>
+        <f>C58*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D59" s="15">
@@ -2002,7 +2002,7 @@
         <v/>
       </c>
       <c r="C60" s="15">
-        <f>C59*(1+MAX(0.1,$B$11))</f>
+        <f>C59*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D60" s="15">
@@ -2028,7 +2028,7 @@
         <v/>
       </c>
       <c r="C61" s="15">
-        <f>C60*(1+MAX(0.1,$B$11))</f>
+        <f>C60*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D61" s="15">
@@ -2054,7 +2054,7 @@
         <v/>
       </c>
       <c r="C62" s="15">
-        <f>C61*(1+MAX(0.1,$B$11))</f>
+        <f>C61*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D62" s="15">
@@ -2080,7 +2080,7 @@
         <v/>
       </c>
       <c r="C63" s="15">
-        <f>C62*(1+MAX(0.1,$B$11))</f>
+        <f>C62*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D63" s="15">
@@ -2106,7 +2106,7 @@
         <v/>
       </c>
       <c r="C64" s="15">
-        <f>C63*(1+MAX(0.1,$B$11))</f>
+        <f>C63*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D64" s="15">
@@ -2132,7 +2132,7 @@
         <v/>
       </c>
       <c r="C65" s="15">
-        <f>C64*(1+MAX(0.1,$B$11))</f>
+        <f>C64*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D65" s="15">
@@ -2158,7 +2158,7 @@
         <v/>
       </c>
       <c r="C66" s="15">
-        <f>C65*(1+MAX(0.1,$B$11))</f>
+        <f>C65*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D66" s="15">
@@ -2184,7 +2184,7 @@
         <v/>
       </c>
       <c r="C67" s="15">
-        <f>C66*(1+MAX(0.1,$B$11))</f>
+        <f>C66*(1+MAX(0.05,$B$11))</f>
         <v/>
       </c>
       <c r="D67" s="15">
@@ -2205,8 +2205,8 @@
     <mergeCell ref="A2:F2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 10% 起跳，請輸入 10% 以上。" type="decimal" operator="greaterThanOrEqual">
-      <formula1>0.1</formula1>
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 5% 起跳，請輸入 5% 以上。" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0.05</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2298,11 +2298,11 @@
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
-          <t>個人／家庭通膨（10% 起跳）</t>
+          <t>個人／家庭通膨（5% 起跳）</t>
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="7">
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="F7" s="13">
-        <f>(1+F5)/(1+MAX(0.1,F6))-1</f>
+        <f>(1+F5)/(1+MAX(0.05,F6))-1</f>
         <v/>
       </c>
     </row>
@@ -2432,8 +2432,8 @@
     <mergeCell ref="A2:F2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="本工具假設台灣個人通膨每年 10% 起跳，請輸入 10% 以上。" type="decimal" operator="greaterThanOrEqual">
-      <formula1>0.1</formula1>
+    <dataValidation sqref="F6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="本工具假設台灣個人通膨每年 5% 起跳，請輸入 5% 以上。" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0.05</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
